--- a/business_forms/042_data_storage_billing_form--business_forms.xlsx
+++ b/business_forms/042_data_storage_billing_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>billing_details</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Billing Details</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter your billing information</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +552,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>client_details</t>
+          <t>Client Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,13 +575,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Payment Method</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select a payment method</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +602,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +625,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>date_of_service</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter the date of service</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,36 +652,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>time_of_service</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Time of Service</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter the time of service</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter your email</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,41 +701,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter your phone number</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>confirm_payment_status</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Confirm Payment Status</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +751,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>confirm</t>
+          <t>subscription_status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>confirm</t>
+          <t>Subscription Status</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +774,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>confirm_note</t>
+          <t>confirm_phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>confirm_note</t>
+          <t>Confirm Phone Number</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,13 +802,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>confirm_email</t>
+          <t>Confirm Email</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +820,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>confirm_phone</t>
+          <t>confirm_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>confirm_phone</t>
+          <t>Confirm Date of Service</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +843,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>confirm_date</t>
+          <t>confirm_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>confirm_date</t>
+          <t>Confirm Time of Service</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +866,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>confirm_payment_method</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>Confirm Payment Method</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +889,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>subscription_status</t>
+          <t>confirm_subscription_status</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>subscription_status</t>
+          <t>Confirm Subscription Status</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,18 +912,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>confirm_amount</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>Confirm Amount</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,179 +935,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>confirm_note</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>Confirm Note</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>subscription_status</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>subscription_status</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>subscription_status</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>subscription_status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>subscription_status</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>subscription_status</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>subscription_status</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>subscription_status</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +961,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1211,136 +1074,136 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>confirm_choices</t>
+          <t>confirm_payment_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>confirm_choices</t>
+          <t>confirm_payment_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>confirm_note_choices</t>
+          <t>subscription_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>confirm_note_choices</t>
+          <t>subscription_status_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>confirm_email_choices</t>
+          <t>confirm_phone_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>confirm_email_choices</t>
+          <t>confirm_phone_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>confirm_phone_choices</t>
+          <t>confirm_email_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>confirm_phone_choices</t>
+          <t>confirm_email_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1215,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1369,87 +1232,87 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>confirm_time_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>confirm_time_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>subscription_status_choices</t>
+          <t>confirm_payment_method_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>subscription_status_choices</t>
+          <t>confirm_payment_method_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>confirm_subscription_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1329,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>confirm_subscription_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,272 +1346,68 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>confirm_amount_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>confirm_amount_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>subscription_status_choices</t>
+          <t>confirm_note_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>subscription_status_choices</t>
+          <t>confirm_note_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>subscription_status_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>subscription_status_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>subscription_status_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>subscription_status_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>subscription_status_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>subscription_status_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Inactive</t>
         </is>
       </c>
     </row>
